--- a/data/examples/output_example_formulas.xlsx
+++ b/data/examples/output_example_formulas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,323 +1116,66 @@
       </c>
     </row>
     <row r="13">
-      <c r="E13">
-        <f>SUM(F13:R13)</f>
-        <v/>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Engineers capacity</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14">
-        <f>SUM(F14:R14)</f>
-        <v/>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Managers capacity</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E15">
-        <f>SUM(F15:R15)</f>
-        <v/>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Engineers absence</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16">
-        <f>SUM(F16:R16)</f>
-        <v/>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Managers absence</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E17">
-        <f>SUM(F17:R17)</f>
-        <v/>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Weekly Allocation</t>
         </is>
       </c>
-      <c r="F18">
-        <f>SUM(F8:F17)</f>
-        <v/>
-      </c>
-      <c r="G18">
-        <f>SUM(G8:G17)</f>
-        <v/>
-      </c>
-      <c r="H18">
-        <f>SUM(H8:H17)</f>
-        <v/>
-      </c>
-      <c r="I18">
-        <f>SUM(I8:I17)</f>
-        <v/>
-      </c>
-      <c r="J18">
-        <f>SUM(J8:J17)</f>
-        <v/>
-      </c>
-      <c r="K18">
-        <f>SUM(K8:K17)</f>
-        <v/>
-      </c>
-      <c r="L18">
-        <f>SUM(L8:L17)</f>
-        <v/>
-      </c>
-      <c r="M18">
-        <f>SUM(M8:M17)</f>
-        <v/>
-      </c>
-      <c r="N18">
-        <f>SUM(N8:N17)</f>
-        <v/>
-      </c>
-      <c r="O18">
-        <f>SUM(O8:O17)</f>
-        <v/>
-      </c>
-      <c r="P18">
-        <f>SUM(P8:P17)</f>
-        <v/>
-      </c>
-      <c r="Q18">
-        <f>SUM(Q8:Q17)</f>
-        <v/>
-      </c>
-      <c r="R18">
-        <f>SUM(R8:R17)</f>
+      <c r="F13">
+        <f>SUM(F8:F12)</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>SUM(G8:G12)</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>SUM(H8:H12)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>SUM(I8:I12)</f>
+        <v/>
+      </c>
+      <c r="J13">
+        <f>SUM(J8:J12)</f>
+        <v/>
+      </c>
+      <c r="K13">
+        <f>SUM(K8:K12)</f>
+        <v/>
+      </c>
+      <c r="L13">
+        <f>SUM(L8:L12)</f>
+        <v/>
+      </c>
+      <c r="M13">
+        <f>SUM(M8:M12)</f>
+        <v/>
+      </c>
+      <c r="N13">
+        <f>SUM(N8:N12)</f>
+        <v/>
+      </c>
+      <c r="O13">
+        <f>SUM(O8:O12)</f>
+        <v/>
+      </c>
+      <c r="P13">
+        <f>SUM(P8:P12)</f>
+        <v/>
+      </c>
+      <c r="Q13">
+        <f>SUM(Q8:Q12)</f>
+        <v/>
+      </c>
+      <c r="R13">
+        <f>SUM(R8:R12)</f>
         <v/>
       </c>
     </row>

--- a/data/examples/output_example_formulas.xlsx
+++ b/data/examples/output_example_formulas.xlsx
@@ -561,43 +561,43 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="4">
@@ -832,43 +832,43 @@
         <v/>
       </c>
       <c r="F8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="P8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="R8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="9">

--- a/data/examples/output_example_formulas.xlsx
+++ b/data/examples/output_example_formulas.xlsx
@@ -813,184 +813,184 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Auth &amp; Identity Management</t>
+          <t>Alpha Search</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="E8">
         <f>SUM(F8:R8)</f>
         <v/>
       </c>
       <c r="F8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="G8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="L8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="M8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="O8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="P8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="R8" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Real-time Analytics</t>
+          <t>Beta Platform</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="E9">
         <f>SUM(F9:R9)</f>
         <v/>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mobile App Redesign</t>
+          <t>Gamma Onboarding</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <f>SUM(F10:R10)</f>
         <v/>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -1001,118 +1001,118 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>API Gateway Optimization</t>
+          <t>Delta Infra</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="E11">
         <f>SUM(F11:R11)</f>
         <v/>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Data Quality Framework</t>
+          <t>Epsilon Compliance</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="E12">
         <f>SUM(F12:R12)</f>
         <v/>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13">

--- a/data/examples/output_example_formulas.xlsx
+++ b/data/examples/output_example_formulas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,65 +444,70 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Off Estimate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Mar.30</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Apr.06</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Apr.13</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Apr.20</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Apr.27</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>May.04</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>May.11</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>May.18</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>May.25</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Jun.01</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Jun.08</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Jun.15</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Jun.22</t>
         </is>
@@ -514,9 +519,6 @@
           <t>Engineer Capacity (Bruto)</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>5</v>
-      </c>
       <c r="G2" t="n">
         <v>5</v>
       </c>
@@ -551,6 +553,9 @@
         <v>5</v>
       </c>
       <c r="R2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -560,9 +565,6 @@
           <t>Engineer Absence</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>0.2</v>
-      </c>
       <c r="G3" t="n">
         <v>0.2</v>
       </c>
@@ -597,6 +599,9 @@
         <v>0.2</v>
       </c>
       <c r="R3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S3" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -606,10 +611,6 @@
           <t>Engineer Net Capacity</t>
         </is>
       </c>
-      <c r="F4">
-        <f>F2-F3</f>
-        <v/>
-      </c>
       <c r="G4">
         <f>G2-G3</f>
         <v/>
@@ -658,6 +659,10 @@
         <f>R2-R3</f>
         <v/>
       </c>
+      <c r="S4">
+        <f>S2-S3</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -665,9 +670,6 @@
           <t>Management Capacity</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
@@ -702,6 +704,9 @@
         <v>2</v>
       </c>
       <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -711,9 +716,6 @@
           <t>Management Absence</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>0.3</v>
-      </c>
       <c r="G6" t="n">
         <v>0.3</v>
       </c>
@@ -750,6 +752,9 @@
       <c r="R6" t="n">
         <v>0.3</v>
       </c>
+      <c r="S6" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -757,10 +762,6 @@
           <t>Management Net Capacity</t>
         </is>
       </c>
-      <c r="F7">
-        <f>F5-F6</f>
-        <v/>
-      </c>
       <c r="G7">
         <f>G5-G6</f>
         <v/>
@@ -809,6 +810,10 @@
         <f>R5-R6</f>
         <v/>
       </c>
+      <c r="S7">
+        <f>S5-S6</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -828,47 +833,51 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <f>SUM(F8:R8)</f>
-        <v/>
-      </c>
-      <c r="F8" t="n">
-        <v>0.6</v>
+        <f>SUM(G8:S8)</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>ABS(E8-D8)&gt;0.05</f>
+        <v/>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6</v>
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -889,47 +898,51 @@
         <v>12</v>
       </c>
       <c r="E9">
-        <f>SUM(F9:R9)</f>
-        <v/>
-      </c>
-      <c r="F9" t="n">
-        <v>0.9</v>
+        <f>SUM(G9:S9)</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>ABS(E9-D9)&gt;0.05</f>
+        <v/>
       </c>
       <c r="G9" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9</v>
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -950,11 +963,12 @@
         <v>5</v>
       </c>
       <c r="E10">
-        <f>SUM(F10:R10)</f>
-        <v/>
-      </c>
-      <c r="F10" t="n">
-        <v>0.4</v>
+        <f>SUM(G10:S10)</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>ABS(E10-D10)&gt;0.05</f>
+        <v/>
       </c>
       <c r="G10" t="n">
         <v>0.4</v>
@@ -990,6 +1004,9 @@
         <v>0.4</v>
       </c>
       <c r="R10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -1011,47 +1028,51 @@
         <v>7</v>
       </c>
       <c r="E11">
-        <f>SUM(F11:R11)</f>
-        <v/>
-      </c>
-      <c r="F11" t="n">
-        <v>0.5</v>
+        <f>SUM(G11:S11)</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>ABS(E11-D11)&gt;0.05</f>
+        <v/>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5</v>
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1072,47 +1093,51 @@
         <v>3</v>
       </c>
       <c r="E12">
-        <f>SUM(F12:R12)</f>
-        <v/>
-      </c>
-      <c r="F12" t="n">
-        <v>0.2</v>
+        <f>SUM(G12:S12)</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>ABS(E12-D12)&gt;0.05</f>
+        <v/>
       </c>
       <c r="G12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
         <v>0.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1126,8 +1151,12 @@
           <t>Weekly Allocation</t>
         </is>
       </c>
-      <c r="F13">
-        <f>SUM(F8:F12)</f>
+      <c r="D13">
+        <f>SUM(D8:D12)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>SUM(E8:E12)</f>
         <v/>
       </c>
       <c r="G13">
@@ -1176,6 +1205,69 @@
       </c>
       <c r="R13">
         <f>SUM(R8:R12)</f>
+        <v/>
+      </c>
+      <c r="S13">
+        <f>SUM(S8:S12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Off Capacity</t>
+        </is>
+      </c>
+      <c r="G14">
+        <f>ABS(G13-G4)&gt;0.1</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>ABS(H13-H4)&gt;0.1</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>ABS(I13-I4)&gt;0.1</f>
+        <v/>
+      </c>
+      <c r="J14">
+        <f>ABS(J13-J4)&gt;0.1</f>
+        <v/>
+      </c>
+      <c r="K14">
+        <f>ABS(K13-K4)&gt;0.1</f>
+        <v/>
+      </c>
+      <c r="L14">
+        <f>ABS(L13-L4)&gt;0.1</f>
+        <v/>
+      </c>
+      <c r="M14">
+        <f>ABS(M13-M4)&gt;0.1</f>
+        <v/>
+      </c>
+      <c r="N14">
+        <f>ABS(N13-N4)&gt;0.1</f>
+        <v/>
+      </c>
+      <c r="O14">
+        <f>ABS(O13-O4)&gt;0.1</f>
+        <v/>
+      </c>
+      <c r="P14">
+        <f>ABS(P13-P4)&gt;0.1</f>
+        <v/>
+      </c>
+      <c r="Q14">
+        <f>ABS(Q13-Q4)&gt;0.1</f>
+        <v/>
+      </c>
+      <c r="R14">
+        <f>ABS(R13-R4)&gt;0.1</f>
+        <v/>
+      </c>
+      <c r="S14">
+        <f>ABS(S13-S4)&gt;0.1</f>
         <v/>
       </c>
     </row>

--- a/data/examples/output_example_formulas.xlsx
+++ b/data/examples/output_example_formulas.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Epic / Capacity Metric</t>
+          <t>Epic Description</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Management Capacity</t>
+          <t>Management Capacity (Bruto)</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/data/examples/output_example_formulas.xlsx
+++ b/data/examples/output_example_formulas.xlsx
@@ -52,6 +52,83 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00548235"/>
+          <bgColor rgb="00548235"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00B4C6E7"/>
+          <bgColor rgb="00B4C6E7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D9D2E9"/>
+          <bgColor rgb="00D9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4D6"/>
+          <bgColor rgb="00FCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF2CC"/>
+          <bgColor rgb="00FFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F8CBAD"/>
+          <bgColor rgb="00F8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -519,6 +596,10 @@
           <t>Engineer Capacity (Bruto)</t>
         </is>
       </c>
+      <c r="E2">
+        <f>SUM(G2:S2)</f>
+        <v/>
+      </c>
       <c r="G2" t="n">
         <v>5</v>
       </c>
@@ -565,6 +646,10 @@
           <t>Engineer Absence</t>
         </is>
       </c>
+      <c r="E3">
+        <f>SUM(G3:S3)</f>
+        <v/>
+      </c>
       <c r="G3" t="n">
         <v>0.2</v>
       </c>
@@ -611,6 +696,10 @@
           <t>Engineer Net Capacity</t>
         </is>
       </c>
+      <c r="E4">
+        <f>SUM(G4:S4)</f>
+        <v/>
+      </c>
       <c r="G4">
         <f>G2-G3</f>
         <v/>
@@ -670,6 +759,10 @@
           <t>Management Capacity (Bruto)</t>
         </is>
       </c>
+      <c r="E5">
+        <f>SUM(G5:S5)</f>
+        <v/>
+      </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
@@ -716,6 +809,10 @@
           <t>Management Absence</t>
         </is>
       </c>
+      <c r="E6">
+        <f>SUM(G6:S6)</f>
+        <v/>
+      </c>
       <c r="G6" t="n">
         <v>0.3</v>
       </c>
@@ -762,6 +859,10 @@
           <t>Management Net Capacity</t>
         </is>
       </c>
+      <c r="E7">
+        <f>SUM(G7:S7)</f>
+        <v/>
+      </c>
       <c r="G7">
         <f>G5-G6</f>
         <v/>
@@ -1272,6 +1373,42 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F8:F12">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>F8=TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G14:S14">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+      <formula>G14=TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:S14">
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="0">
+      <formula>$A2="Self-Service ML EV Range - Phase 1"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="0">
+      <formula>$A2="Quality improvements through ML/AI experimentation"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="3" stopIfTrue="0">
+      <formula>$A2="Maintenance &amp; Release"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="4" stopIfTrue="0">
+      <formula>$A2="Security &amp; Compliance"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="5" stopIfTrue="0">
+      <formula>$A2="Customer Support"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="6" stopIfTrue="0">
+      <formula>$A2="Critical Technical Debt"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" dxfId="7" stopIfTrue="0">
+      <formula>$A2="Critical Product Debt"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="8" stopIfTrue="0">
+      <formula>$A2="Critical Customer Commitments"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>